--- a/templates/_masters/LGL-001-str-license-renewal-calendar-BLANK.xlsx
+++ b/templates/_masters/LGL-001-str-license-renewal-calendar-BLANK.xlsx
@@ -523,24 +523,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00166534"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="00B91C1C"/>
-        <sz val="10"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFB3B3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3509,29 +3496,29 @@
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="between" dxfId="2">
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="1">
       <formula>0</formula>
       <formula>29</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" dxfId="3">
+    <cfRule type="cellIs" priority="3" operator="between" dxfId="2">
       <formula>30</formula>
       <formula>89</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="4">
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="3">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:H106">
-    <cfRule type="expression" priority="5" dxfId="5">
+    <cfRule type="expression" priority="5" dxfId="4">
       <formula>ISNUMBER(SEARCH("Expired",$H7))</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="2">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>ISNUMBER(SEARCH("Critical",$H7))</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6">
+    <cfRule type="expression" priority="7" dxfId="5">
       <formula>ISNUMBER(SEARCH("Soon",$H7))</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="7">
+    <cfRule type="expression" priority="8" dxfId="6">
       <formula>ISNUMBER(SEARCH("Active",$H7))</formula>
     </cfRule>
   </conditionalFormatting>
